--- a/manuscript_material/source_data/Source_Data_Fig2.xlsx
+++ b/manuscript_material/source_data/Source_Data_Fig2.xlsx
@@ -426,7 +426,7 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
@@ -441,7 +441,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>difference_galaxy_minus_code</t>
+          <t>condition_difference_galaxy_minus_open_ended_code</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
@@ -456,12 +456,12 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>replicates_open_ended_code</t>
+          <t>replicate_runs_open_ended_code</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>replicates_galaxy</t>
+          <t>replicate_runs_galaxy</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="C5" t="n">
@@ -621,7 +621,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Four configurations, pooled (Codex harness)</t>
+          <t>Four Codex model configurations, pooled</t>
         </is>
       </c>
       <c r="C6" t="n">
@@ -658,7 +658,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro, Claude Code harness (superseded)</t>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -794,7 +794,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -827,7 +827,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Four configurations, pooled (Codex harness)</t>
+          <t>Four Codex model configurations, pooled</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -971,7 +971,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>DeepSeek V4 Pro</t>
+          <t>DeepSeek V4 Pro (Codex)</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1008,7 +1008,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Four configurations, pooled (Codex harness)</t>
+          <t>Four Codex model configurations, pooled</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1059,22 +1059,22 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>environment</t>
+          <t>execution_condition</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>configuration</t>
+          <t>model_configuration</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>replicate</t>
+          <t>replicate_run</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>agreement</t>
+          <t>output_agreement</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -1109,7 +1109,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1316,7 +1316,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1339,7 +1339,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1362,7 +1362,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1385,7 +1385,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1431,7 +1431,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1454,7 +1454,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1477,7 +1477,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1500,7 +1500,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1523,7 +1523,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1569,7 +1569,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1638,7 +1638,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1659,7 +1659,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -1701,7 +1701,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -1724,7 +1724,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -1839,7 +1839,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -1862,7 +1862,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -1885,7 +1885,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -1908,7 +1908,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -1954,7 +1954,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2023,7 +2023,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -2069,7 +2069,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -2092,7 +2092,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -2207,7 +2207,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -2230,7 +2230,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -2253,7 +2253,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -2276,7 +2276,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -2299,7 +2299,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -2345,7 +2345,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -2368,7 +2368,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2391,7 +2391,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2437,7 +2437,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -2460,7 +2460,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2529,7 +2529,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2598,7 +2598,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2644,7 +2644,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -2667,7 +2667,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -2690,7 +2690,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -2713,7 +2713,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2759,7 +2759,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -2828,7 +2828,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -2851,7 +2851,7 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
@@ -2874,7 +2874,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -2897,7 +2897,7 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -2943,7 +2943,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
@@ -3035,7 +3035,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3104,7 +3104,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -3127,7 +3127,7 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -3173,7 +3173,7 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
@@ -3196,7 +3196,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -3242,7 +3242,7 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -3288,7 +3288,7 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -3311,7 +3311,7 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
@@ -3334,7 +3334,7 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
@@ -3357,7 +3357,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -3380,7 +3380,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -3403,7 +3403,7 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
@@ -3449,7 +3449,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
@@ -3472,7 +3472,7 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
@@ -3587,7 +3587,7 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
@@ -3610,7 +3610,7 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
@@ -3633,7 +3633,7 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
@@ -3817,7 +3817,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Open-ended code</t>
+          <t>Open-ended code condition</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -3840,7 +3840,7 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
@@ -3863,7 +3863,7 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
@@ -3886,7 +3886,7 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -3909,7 +3909,7 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -3955,7 +3955,7 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -3978,7 +3978,7 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
@@ -4024,7 +4024,7 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -4047,7 +4047,7 @@
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -4093,7 +4093,7 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
@@ -4185,7 +4185,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
@@ -4277,7 +4277,7 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -4300,7 +4300,7 @@
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
@@ -4323,7 +4323,7 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
@@ -4346,7 +4346,7 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
@@ -4369,7 +4369,7 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -4415,7 +4415,7 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
@@ -4438,7 +4438,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
@@ -4461,7 +4461,7 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
@@ -4484,7 +4484,7 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
@@ -4507,7 +4507,7 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
@@ -4553,7 +4553,7 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -4599,7 +4599,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
@@ -4668,7 +4668,7 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -4737,7 +4737,7 @@
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -4783,7 +4783,7 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
@@ -4806,7 +4806,7 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
@@ -4829,7 +4829,7 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
@@ -4875,7 +4875,7 @@
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -4898,7 +4898,7 @@
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
@@ -4921,7 +4921,7 @@
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -4967,7 +4967,7 @@
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
@@ -4990,7 +4990,7 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
@@ -5059,7 +5059,7 @@
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
@@ -5082,7 +5082,7 @@
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
@@ -5105,7 +5105,7 @@
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
@@ -5174,7 +5174,7 @@
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
@@ -5197,7 +5197,7 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
@@ -5220,7 +5220,7 @@
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
@@ -5266,7 +5266,7 @@
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
@@ -5289,7 +5289,7 @@
       </c>
       <c r="B185" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C185" t="inlineStr">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -5335,7 +5335,7 @@
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
@@ -5358,7 +5358,7 @@
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
@@ -5381,7 +5381,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="B190" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C190" t="inlineStr">
@@ -5427,7 +5427,7 @@
       </c>
       <c r="B191" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C191" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="B192" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C192" t="inlineStr">
@@ -5473,7 +5473,7 @@
       </c>
       <c r="B193" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C193" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="B194" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C194" t="inlineStr">
@@ -5519,7 +5519,7 @@
       </c>
       <c r="B195" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C195" t="inlineStr">
@@ -5542,7 +5542,7 @@
       </c>
       <c r="B196" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C196" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="B197" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C197" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="B198" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C198" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="B200" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C200" t="inlineStr">
@@ -5657,7 +5657,7 @@
       </c>
       <c r="B201" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C201" t="inlineStr">
@@ -5680,7 +5680,7 @@
       </c>
       <c r="B202" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C202" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="B203" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C203" t="inlineStr">
@@ -5726,7 +5726,7 @@
       </c>
       <c r="B204" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C204" t="inlineStr">
@@ -5749,7 +5749,7 @@
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -5772,7 +5772,7 @@
       </c>
       <c r="B206" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C206" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="B207" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C207" t="inlineStr">
@@ -5818,7 +5818,7 @@
       </c>
       <c r="B208" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C208" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="B209" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C209" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="B211" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C211" t="inlineStr">
@@ -5910,7 +5910,7 @@
       </c>
       <c r="B212" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C212" t="inlineStr">
@@ -5933,7 +5933,7 @@
       </c>
       <c r="B213" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C213" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
@@ -6002,7 +6002,7 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -6048,7 +6048,7 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
@@ -6071,7 +6071,7 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -6094,7 +6094,7 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -6140,7 +6140,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -6163,7 +6163,7 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -6186,7 +6186,7 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
@@ -6209,7 +6209,7 @@
       </c>
       <c r="B225" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C225" t="inlineStr">
@@ -6232,7 +6232,7 @@
       </c>
       <c r="B226" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C226" t="inlineStr">
@@ -6255,7 +6255,7 @@
       </c>
       <c r="B227" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C227" t="inlineStr">
@@ -6278,7 +6278,7 @@
       </c>
       <c r="B228" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C228" t="inlineStr">
@@ -6301,7 +6301,7 @@
       </c>
       <c r="B229" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C229" t="inlineStr">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="B230" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C230" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="B231" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C231" t="inlineStr">
@@ -6370,7 +6370,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -6393,7 +6393,7 @@
       </c>
       <c r="B233" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C233" t="inlineStr">
@@ -6416,7 +6416,7 @@
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="B235" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C235" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -6485,7 +6485,7 @@
       </c>
       <c r="B237" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C237" t="inlineStr">
@@ -6508,7 +6508,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
@@ -6554,7 +6554,7 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>Galaxy</t>
+          <t>Galaxy condition</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
@@ -6626,7 +6626,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Open-ended code: primary cause</t>
+          <t>Open-ended code condition: primary cause</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -6641,7 +6641,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Open-ended code: primary cause</t>
+          <t>Open-ended code condition: primary cause</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -6656,7 +6656,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Open-ended code: primary cause</t>
+          <t>Open-ended code condition: primary cause</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -6671,7 +6671,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Open-ended code: primary cause</t>
+          <t>Open-ended code condition: primary cause</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -6686,7 +6686,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Open-ended code: primary cause</t>
+          <t>Open-ended code condition: primary cause</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -6701,7 +6701,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Open-ended code: primary cause</t>
+          <t>Open-ended code condition: primary cause</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -6716,7 +6716,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Galaxy: primary cause</t>
+          <t>Galaxy condition: primary cause</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -6731,7 +6731,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Galaxy: primary cause</t>
+          <t>Galaxy condition: primary cause</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -6746,7 +6746,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Galaxy: primary cause</t>
+          <t>Galaxy condition: primary cause</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -6761,7 +6761,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Galaxy: primary cause</t>
+          <t>Galaxy condition: primary cause</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -6776,7 +6776,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Galaxy: primary cause</t>
+          <t>Galaxy condition: primary cause</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -6791,7 +6791,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Galaxy: primary cause</t>
+          <t>Galaxy condition: primary cause</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -6806,7 +6806,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Open-ended code: secondary cause</t>
+          <t>Open-ended code condition: secondary cause</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6821,7 +6821,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Open-ended code: secondary cause</t>
+          <t>Open-ended code condition: secondary cause</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6836,7 +6836,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Open-ended code: secondary cause</t>
+          <t>Open-ended code condition: secondary cause</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -6851,7 +6851,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Open-ended code: secondary cause</t>
+          <t>Open-ended code condition: secondary cause</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -6866,7 +6866,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Galaxy: secondary cause</t>
+          <t>Galaxy condition: secondary cause</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -6881,7 +6881,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Galaxy: secondary cause</t>
+          <t>Galaxy condition: secondary cause</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -6896,7 +6896,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Galaxy: secondary cause</t>
+          <t>Galaxy condition: secondary cause</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -6911,7 +6911,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Galaxy: secondary cause</t>
+          <t>Galaxy condition: secondary cause</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">

--- a/manuscript_material/source_data/Source_Data_Fig2.xlsx
+++ b/manuscript_material/source_data/Source_Data_Fig2.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a-c_differences" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d_IWC_runs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="e_root_causes" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="a_IWC_levels_differences" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_IWC_runs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="b_IWC_task_means" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="c_BixBench_levels_differences" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d_CompBio_levels_differences" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -415,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I17"/>
+  <dimension ref="A1:K6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -464,11 +466,21 @@
           <t>replicate_runs_galaxy</t>
         </is>
       </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>open_ended_code_median_nine_tasks</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>galaxy_median_nine_tasks</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>IWC</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -477,35 +489,41 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>87.33329999999999</v>
+        <v>0.8675</v>
       </c>
       <c r="D2" t="n">
-        <v>89.33329999999999</v>
+        <v>0.9493</v>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>0.0818</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.004</v>
       </c>
       <c r="G2" t="n">
-        <v>5.3</v>
+        <v>0.2232</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>88; 88; 86</t>
+          <t>0.7758; 0.958; 0.8688</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>88; 90; 90</t>
-        </is>
+          <t>0.8779; 0.9781; 0.992</t>
+        </is>
+      </c>
+      <c r="J2" t="n">
+        <v>0.9997121189449684</v>
+      </c>
+      <c r="K2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>IWC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -514,35 +532,41 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>86.66670000000001</v>
+        <v>0.9881</v>
       </c>
       <c r="D3" t="n">
-        <v>88.66670000000001</v>
+        <v>0.9895</v>
       </c>
       <c r="E3" t="n">
-        <v>2</v>
+        <v>0.0014</v>
       </c>
       <c r="F3" t="n">
-        <v>-5.07</v>
+        <v>-0.0058</v>
       </c>
       <c r="G3" t="n">
-        <v>9.52</v>
+        <v>0.0094</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>86; 88; 86</t>
+          <t>0.9853; 0.9877; 0.9913</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>88; 90; 88</t>
-        </is>
+          <t>0.9919; 0.9927; 0.9837</t>
+        </is>
+      </c>
+      <c r="J3" t="n">
+        <v>0.9997121189449684</v>
+      </c>
+      <c r="K3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>IWC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -551,35 +575,41 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>86</v>
+        <v>0.9828</v>
       </c>
       <c r="D4" t="n">
-        <v>86</v>
+        <v>0.9837</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.001</v>
       </c>
       <c r="F4" t="n">
-        <v>-7.05</v>
+        <v>-0.0034</v>
       </c>
       <c r="G4" t="n">
-        <v>6.25</v>
+        <v>0.0076</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>86; 90; 82</t>
+          <t>0.985; 0.9955; 0.9677</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>90; 84; 84</t>
-        </is>
+          <t>0.9892; 0.9794; 0.9825</t>
+        </is>
+      </c>
+      <c r="J4" t="n">
+        <v>1</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.997889272394358</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>IWC</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -588,35 +618,41 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>80.66670000000001</v>
+        <v>0.9224</v>
       </c>
       <c r="D5" t="n">
-        <v>82</v>
+        <v>0.9992</v>
       </c>
       <c r="E5" t="n">
-        <v>1.33</v>
+        <v>0.07679999999999999</v>
       </c>
       <c r="F5" t="n">
-        <v>-5.43</v>
+        <v>0.0019</v>
       </c>
       <c r="G5" t="n">
-        <v>7.8</v>
+        <v>0.1849</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>80; 80; 82</t>
+          <t>0.9923; 0.887; 0.888</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>82; 80; 84</t>
-        </is>
+          <t>0.9999; 0.9991; 0.9986</t>
+        </is>
+      </c>
+      <c r="J5" t="n">
+        <v>1</v>
+      </c>
+      <c r="K5" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BixBench-Verified-50</t>
+          <t>IWC</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -625,417 +661,32 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>85.16670000000001</v>
+        <v>0.9402</v>
       </c>
       <c r="D6" t="n">
-        <v>86.5</v>
+        <v>0.9804</v>
       </c>
       <c r="E6" t="n">
-        <v>1.33</v>
+        <v>0.0402</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.48</v>
+        <v>0.0095</v>
       </c>
       <c r="G6" t="n">
-        <v>6.34</v>
+        <v>0.0775</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>88; 88; 86; 86; 88; 86; 86; 90; 82; 80; 80; 82</t>
+          <t>0.7758; 0.958; 0.8688; 0.9853; 0.9877; 0.9913; 0.985; 0.9955; 0.9677; 0.9923; 0.887; 0.888</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>88; 90; 90; 88; 90; 88; 90; 84; 84; 82; 80; 84</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>BixBench-Verified-50</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>69.33329999999999</v>
-      </c>
-      <c r="D7" t="n">
-        <v>80</v>
-      </c>
-      <c r="E7" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="G7" t="n">
-        <v>21.15</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>70; 68; 70</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>80; 76; 84</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>GPT-5.5</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>86.33329999999999</v>
-      </c>
-      <c r="D8" t="n">
-        <v>86.66670000000001</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.3333</v>
-      </c>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>87; 88; 84</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>84; 89; 87</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>GPT-5.6 Sol</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>91</v>
-      </c>
-      <c r="D9" t="n">
-        <v>91.66670000000001</v>
-      </c>
-      <c r="E9" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>88; 90; 95</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>93; 91; 91</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>GPT-5.6 Luna</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>85</v>
-      </c>
-      <c r="D10" t="n">
-        <v>85</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>84; 86; 85</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>86; 84; 85</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>84.33329999999999</v>
-      </c>
-      <c r="D11" t="n">
-        <v>84.33329999999999</v>
-      </c>
-      <c r="E11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>80; 87; 86</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>83; 87; 83</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CompBioBench</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Four Codex model configurations, pooled</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>86.66670000000001</v>
-      </c>
-      <c r="D12" t="n">
-        <v>86.91670000000001</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>87; 88; 84; 88; 90; 95; 84; 86; 85; 80; 87; 86</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>84; 89; 87; 93; 91; 91; 86; 84; 85; 83; 87; 83</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>GPT-5.5</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.8675</v>
-      </c>
-      <c r="D13" t="n">
-        <v>0.9493</v>
-      </c>
-      <c r="E13" t="n">
-        <v>0.0818</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.004</v>
-      </c>
-      <c r="G13" t="n">
-        <v>0.2232</v>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0.7758; 0.958; 0.8688</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0.8779; 0.9781; 0.992</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>GPT-5.6 Sol</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.9881</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.9895</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0014</v>
-      </c>
-      <c r="F14" t="n">
-        <v>-0.0058</v>
-      </c>
-      <c r="G14" t="n">
-        <v>0.0094</v>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0.9853; 0.9877; 0.9913</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0.9919; 0.9927; 0.9837</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>GPT-5.6 Luna</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.9828</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.9837</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.001</v>
-      </c>
-      <c r="F15" t="n">
-        <v>-0.0034</v>
-      </c>
-      <c r="G15" t="n">
-        <v>0.0076</v>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.985; 0.9955; 0.9677</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0.9892; 0.9794; 0.9825</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>DeepSeek V4 Pro (Codex)</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.9224</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.9992</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.07679999999999999</v>
-      </c>
-      <c r="F16" t="n">
-        <v>0.0019</v>
-      </c>
-      <c r="G16" t="n">
-        <v>0.1849</v>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0.9923; 0.887; 0.888</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0.9999; 0.9991; 0.9986</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>IWC</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Four Codex model configurations, pooled</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.9402</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.9804</v>
-      </c>
-      <c r="E17" t="n">
-        <v>0.0402</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.0095</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0.0775</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>0.7758; 0.958; 0.8688; 0.9853; 0.9877; 0.9913; 0.985; 0.9955; 0.9677; 0.9923; 0.887; 0.888</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
           <t>0.8779; 0.9781; 0.992; 0.9919; 0.9927; 0.9837; 0.9892; 0.9794; 0.9825; 0.9999; 0.9991; 0.9986</t>
         </is>
       </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6603,324 +6254,663 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C21"/>
+  <dimension ref="A1:C11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>bar</t>
+          <t>task</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>cause</t>
+          <t>open_ended_code_mean</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>runs</t>
+          <t>galaxy_mean</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Open-ended code condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Task under-specified or reference ambiguous</t>
-        </is>
+          <t>wf_001_short_read_qc_trim</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>0.9997</v>
       </c>
       <c r="C2" t="n">
-        <v>64</v>
+        <v>0.9989</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Open-ended code condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Statistical or reasoning error</t>
-        </is>
+          <t>wf_002_rnaseq_de_visualization</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
       </c>
       <c r="C3" t="n">
-        <v>39</v>
+        <v>0.9995000000000001</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Open-ended code condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Evaluator rejected a correct answer</t>
-        </is>
+          <t>wf_003_host_contamination_removal</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
       </c>
       <c r="C4" t="n">
-        <v>18</v>
+        <v>0.8788</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Open-ended code condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Missing domain knowledge</t>
-        </is>
+          <t>wf_005_amplicon_dada2_pe_denoising</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.7967</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>0.9586</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Open-ended code condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>No answer submitted</t>
-        </is>
+          <t>wf_006_atacseq_chromatin_accessibility</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.9903</v>
       </c>
       <c r="C6" t="n">
-        <v>1</v>
+        <v>0.9978</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Open-ended code condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Output format violated</t>
-        </is>
+          <t>wf_007_vgp_mitogenome_assembly</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.8255</v>
       </c>
       <c r="C7" t="n">
-        <v>1</v>
+        <v>0.9133</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Galaxy condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Task under-specified or reference ambiguous</t>
-        </is>
+          <t>wf_008_amr_gene_detection</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
       </c>
       <c r="C8" t="n">
-        <v>58</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Galaxy condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Statistical or reasoning error</t>
-        </is>
+          <t>wf_009_clinicalmp_peptide_verification</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>0.9394</v>
       </c>
       <c r="C9" t="n">
-        <v>26</v>
+        <v>0.9579</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Galaxy condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Evaluator rejected a correct answer</t>
-        </is>
+          <t>wf_010_pseudobulk_scrna_de</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.9102</v>
       </c>
       <c r="C10" t="n">
-        <v>15</v>
+        <v>0.9979</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Galaxy condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Missing domain knowledge</t>
-        </is>
+          <t>wf_011_bioproject_metadata_sequence_retrieval</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Galaxy condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>No answer submitted</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Galaxy condition: primary cause</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Platform or tool defect (Galaxy or local software)</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Open-ended code condition: secondary cause</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Task under-specified or reference ambiguous</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Open-ended code condition: secondary cause</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Statistical or reasoning error</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Open-ended code condition: secondary cause</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Evaluator rejected a correct answer</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Open-ended code condition: secondary cause</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Missing domain knowledge</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Galaxy condition: secondary cause</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Task under-specified or reference ambiguous</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Galaxy condition: secondary cause</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Statistical or reasoning error</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Galaxy condition: secondary cause</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Missing domain knowledge</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Galaxy condition: secondary cause</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Platform or tool defect (Galaxy or local software)</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>18</v>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>model_configuration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open_ended_code_mean</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>galaxy_mean</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>condition_difference_galaxy_minus_open_ended_code</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ci_low</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ci_high</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>replicate_runs_open_ended_code</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>replicate_runs_galaxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>87.33329999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>89.33329999999999</v>
+      </c>
+      <c r="E2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0</v>
+      </c>
+      <c r="G2" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>88; 88; 86</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>88; 90; 90</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>86.66670000000001</v>
+      </c>
+      <c r="D3" t="n">
+        <v>88.66670000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>2</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-5.07</v>
+      </c>
+      <c r="G3" t="n">
+        <v>9.52</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>86; 88; 86</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>88; 90; 88</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>86</v>
+      </c>
+      <c r="D4" t="n">
+        <v>86</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="n">
+        <v>-7.05</v>
+      </c>
+      <c r="G4" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>86; 90; 82</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>90; 84; 84</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>80.66670000000001</v>
+      </c>
+      <c r="D5" t="n">
+        <v>82</v>
+      </c>
+      <c r="E5" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F5" t="n">
+        <v>-5.43</v>
+      </c>
+      <c r="G5" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>80; 80; 82</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>82; 80; 84</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Four Codex model configurations, pooled</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>85.16670000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>86.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="F6" t="n">
+        <v>-3.48</v>
+      </c>
+      <c r="G6" t="n">
+        <v>6.34</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>88; 88; 86; 86; 88; 86; 86; 90; 82; 80; 80; 82</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>88; 90; 90; 88; 90; 88; 90; 84; 84; 82; 80; 84</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BixBench-Verified-50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Claude Code, superseded)</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>69.33329999999999</v>
+      </c>
+      <c r="D7" t="n">
+        <v>80</v>
+      </c>
+      <c r="E7" t="n">
+        <v>10.67</v>
+      </c>
+      <c r="F7" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="G7" t="n">
+        <v>21.15</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>70; 68; 70</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>80; 76; 84</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>benchmark</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>model_configuration</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>open_ended_code_mean</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>galaxy_mean</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>condition_difference_galaxy_minus_open_ended_code</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>ci_low</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>ci_high</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>replicate_runs_open_ended_code</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>replicate_runs_galaxy</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GPT-5.5</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>86.33329999999999</v>
+      </c>
+      <c r="D2" t="n">
+        <v>86.66670000000001</v>
+      </c>
+      <c r="E2" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>87; 88; 84</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>84; 89; 87</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Sol</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>91</v>
+      </c>
+      <c r="D3" t="n">
+        <v>91.66670000000001</v>
+      </c>
+      <c r="E3" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>88; 90; 95</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>93; 91; 91</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GPT-5.6 Luna</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>85</v>
+      </c>
+      <c r="D4" t="n">
+        <v>85</v>
+      </c>
+      <c r="E4" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>84; 86; 85</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>86; 84; 85</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DeepSeek V4 Pro (Codex)</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>84.33329999999999</v>
+      </c>
+      <c r="D5" t="n">
+        <v>84.33329999999999</v>
+      </c>
+      <c r="E5" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>80; 87; 86</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>83; 87; 83</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CompBioBench</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Four Codex model configurations, pooled</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>86.66670000000001</v>
+      </c>
+      <c r="D6" t="n">
+        <v>86.91670000000001</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>87; 88; 84; 88; 90; 95; 84; 86; 85; 80; 87; 86</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>84; 89; 87; 93; 91; 91; 86; 84; 85; 83; 87; 83</t>
+        </is>
       </c>
     </row>
   </sheetData>
